--- a/docs/Bizboard_SaaS_Readiness_Checklist.xlsx
+++ b/docs/Bizboard_SaaS_Readiness_Checklist.xlsx
@@ -687,7 +687,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Status as of 2026-10-23 (deep-review fixes recorded) from repo evidence. Nothing is proven on hosted staging yet; HO-n = people item n in docs/roadmap/SAAS_READINESS_HANDOVER_2026-10-22.md.</t>
+          <t>Status as of 2026-10-23 (deep-review fixes + ops pass recorded; 2026-10-24: 10 engineering items closed, BB-100 walk-through, second pass and F10 done; decisions D-01..D-20 in docs/roadmap/DECISIONS_2026-10-24.md, sign-off pack drafted for 15) from repo evidence. Nothing is proven on hosted staging yet; HO-n = people item n in docs/roadmap/SAAS_READINESS_HANDOVER_2026-10-22.md.</t>
         </is>
       </c>
     </row>
@@ -1157,7 +1157,7 @@
       <c r="G5" s="10" t="n"/>
       <c r="H5" s="10" t="inlineStr">
         <is>
-          <t>docs/FREEZE_SCOPE.md; docs/requirements/; 51 journey cells; golden e2e as executable spec</t>
+          <t>docs/FREEZE_SCOPE.md; docs/requirements/; 51 journey cells; golden e2e as executable spec; docs/requirements/REQUIREMENTS_BASELINE.md</t>
         </is>
       </c>
       <c r="I5" s="10" t="n"/>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="K5" s="10" t="inlineStr">
         <is>
-          <t>Spread across freeze scope, plans and tests; no single signed requirements doc.</t>
+          <t>Spread across freeze scope, plans and tests; no single signed requirements doc.; 2026-10-24 A/B pass: Release-1 requirements baseline written (scope, additions since freeze, flags, limits, rules, NFRs). Awaiting founder signature.; 2026-10-25: baseline already consolidated in docs/requirements/REQUIREMENTS_BASELINE.md (sign-off pack B-14); awaiting founder signature only.</t>
         </is>
       </c>
     </row>
@@ -1206,7 +1206,7 @@
       <c r="G6" s="10" t="n"/>
       <c r="H6" s="10" t="inlineStr">
         <is>
-          <t>billing module: plans, trial, quotas, entitlements</t>
+          <t>billing module: plans, trial, quotas, entitlements; docs/roadmap/SIGNOFF_PACK_2026-10-23.md B-1, B-2</t>
         </is>
       </c>
       <c r="I6" s="10" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="K6" s="10" t="inlineStr">
         <is>
-          <t>Mechanism built. Prices, trial length and limits not signed by founder.</t>
+          <t>Mechanism built. Prices, trial length and limits not signed by founder.; 2026-10-24 A/B pass: Plans/prices (₹0/499/1,499/4,999) and 14-day trial proposed from the seeded values. Awaiting founder signature (CA for SaaS GST).; 2026-10-25: found - seeded paid plans switch the GSTR-1/3B worksheets off (ENABLE_GSTR in FREEZE_DARK_PLAN_MODULES) while the trial has them, so an upgrading customer would lose them. Awaiting founder decision on which paid plans include them.; 2026-10-25 (D-16): GST worksheets (GSTR-1/3B) granted on all four plans, like the trial (freeze_safe_modules + migration billing 0021). Prices still unsigned.</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="K9" s="10" t="inlineStr">
         <is>
-          <t>Open: CA sign-off, hosted run, browser check, PB-01..03.</t>
+          <t>2026-10-24: browser check done (purchase bill with a new supplier on local staging: totals, payable and stock correct; BB100_JOURNEY_WALKTHROUGH_2026-10-24.md); purchase orders now take the HSN-table GST rate like bills. Left: CA sign-off, hosted run, PB-01 (CA question), PB-02/PB-03 already fixed (searchable supplier filter on planning, paged server-searched supplier list).</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E12" s="10" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F12" s="10" t="inlineStr">
@@ -1512,7 +1512,7 @@
       <c r="G12" s="10" t="n"/>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>docs/requirements/ITEM_STOCK_GODOWN_EXPIRY.md; inventory suites</t>
+          <t>docs/requirements/ITEM_STOCK_GODOWN_EXPIRY.md; inventory suites; 115 batch/serial/expiry/FEFO tests pass (test_inventory_serials_wp02.py, test_wave15_fefo.py, test_inventory_idr06_expiry.py and 9 more)</t>
         </is>
       </c>
       <c r="I12" s="10" t="n"/>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="K12" s="10" t="inlineStr">
         <is>
-          <t>Batch/expiry supported. FIFO not supported: stock cost is weighted average (documented on /limits, key 'cost').</t>
+          <t>Batch/expiry supported. FIFO not supported: stock cost is weighted average (documented on /limits, key 'cost').; 2026-10-24 A/B pass: Batch, serial and expiry verified; FIFO layers are a documented limitation (weighted average, /limits "cost").</t>
         </is>
       </c>
     </row>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="K18" s="10" t="inlineStr">
         <is>
-          <t>Large part of the tree not yet through CI; not run on hosted staging.</t>
+          <t>Large part of the tree not yet through CI; not run on hosted staging.; 2026-10-25 (WP, LLM plan): All blocking CI gates run locally (D-20: no commit): ruff, web lint/tsc, migrations check, help codes, register claims, guards, OpenAPI/types regenerated, web build + SW + bundle budget, npm audit/pip-audit clean, 406 web test files pass, backend on Postgres 6975 passed; the 52 that failed under 4-worker load re-run serially: 173/175 pass, the 2 left are timing limits only (Complete 2.7 s vs 2.5 s; 5,000-product index) while another session's mutation run used ~4 CPU cores - CI decides, diff coverage 92%. Left: commit go-ahead and green CI.</t>
         </is>
       </c>
     </row>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="K23" s="10" t="inlineStr">
         <is>
-          <t>No CA has filed from these worksheets yet.</t>
+          <t>No CA has filed from these worksheets yet.; 2026-10-24: bills of supply missing from GSTR-1 Table 8/13 and GSTR-3B 3.1(c)/(e) - options note for the CA in docs/ca/F2_BILLS_OF_SUPPLY_IN_GST_RETURNS.md (D-09: no code change until the CA decides).; 2026-10-25 (D-14): bills-of-supply treatment (options B+A) built behind GST_BILL_OF_SUPPLY_RETURNS, off for every company until the CA agrees; test_bill_of_supply_returns.py.</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="K27" s="10" t="inlineStr">
         <is>
-          <t>CA not yet engaged.</t>
+          <t>CA not yet engaged.; 2026-10-24: CA_SIGN_OFF_CHECKLIST.md row R1 added (bills of supply).</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="K29" s="10" t="inlineStr">
         <is>
-          <t>Proven locally only; needs the tenancy + RLS suites against a hosted DB.</t>
+          <t>Proven locally only; needs the tenancy + RLS suites against a hosted DB.; 2026-10-24: Postgres-only suites (row-level security, concurrency, tenancy) re-run on a fresh local Postgres: 543 passed, 1 skipped. Still to run on the hosted database.</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="K30" s="10" t="inlineStr">
         <is>
-          <t>Hosted-staging run and independent pentest pending.</t>
+          <t>Hosted-staging run and independent pentest pending.; 2026-10-25 (WP, LLM plan): Live cross-tenant probe through nginx with RLS on (scripts/security/tenant_probe.py): 0 leaks on reads and list filters; writes naming the other company refused (400). Sales-staff logins only; owner roles left to the pentest and the Postgres tenancy suites.</t>
         </is>
       </c>
     </row>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="K31" s="10" t="inlineStr">
         <is>
-          <t>Proven in repo; hosted run pending.; 2026-10-23 review: Fixed: rls_bypass() did not nest, so staff admin lists (TDS claims, ownership transfers) were empty on Postgres; shared bypass admin mixin.</t>
+          <t>Proven in repo; hosted run pending.; 2026-10-23 review: Fixed: rls_bypass() did not nest, so staff admin lists (TDS claims, ownership transfers) were empty on Postgres; shared bypass admin mixin.; 2026-10-24: Postgres-only suites (row-level security, concurrency, tenancy) re-run on a fresh local Postgres: 543 passed, 1 skipped. Still to run on the hosted database.</t>
         </is>
       </c>
     </row>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="K35" s="10" t="inlineStr">
         <is>
-          <t>Retention policy needs counsel sign-off.; 2026-10-23 review: Export no longer stuck PENDING forever; streamed to disk; all 12 pinned sections now really pinned in the column snapshot.</t>
+          <t>Retention policy needs counsel sign-off.; 2026-10-23 review: Export no longer stuck PENDING forever; streamed to disk; all 12 pinned sections now really pinned in the column snapshot.; 2026-10-25: retention period now configurable per company (D-13); see BB-070.</t>
         </is>
       </c>
     </row>
@@ -3249,7 +3249,7 @@
       </c>
       <c r="K46" s="10" t="inlineStr">
         <is>
-          <t>Independent pentest on hosted staging not done.</t>
+          <t>Independent pentest on hosted staging not done.; 2026-10-23 ops pass: Two security fixes this pass: spoofable client IP in rate limits; permanent-lockout counter race (see BB-046). Pentest still pending.; 2026-10-25 (WP, LLM plan): Local ZAP baseline + signed-in API scan (7 batches) + cross-tenant probe: 0 injection, 0 cross-tenant read/write; ZAP SQLi alerts proven false positives (rate-limit 503s); fixed missing Permissions-Policy/COOP/CORP headers and HTML 404s on /api/ (docs/security/LOCAL_SCAN_2026-10-25.md). Pentest brief ready (docs/security/PENTEST_SCOPE.md). Left: independent pentest on hosted staging.</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       <c r="G47" s="10" t="n"/>
       <c r="H47" s="10" t="inlineStr">
         <is>
-          <t>DRF throttles (otp, sensitive_action, public_link); SMS guard (test_sms_guard.py); bot check (test_bot_check.py); test_public_pay_rate_limit.py; test_saas_review_fixes.py (SMS, Turnstile)</t>
+          <t>DRF throttles (otp, sensitive_action, public_link); SMS guard (test_sms_guard.py); bot check (test_bot_check.py); test_public_pay_rate_limit.py; test_saas_review_fixes.py (SMS, Turnstile); NUM_PROXIES = NUM_TRUSTED_PROXIES (test_throttle_client_ip.py); core/services/counters.py TTL fix (test_cache_counters_ttl.py)</t>
         </is>
       </c>
       <c r="I47" s="10" t="inlineStr">
@@ -3302,7 +3302,7 @@
       </c>
       <c r="K47" s="10" t="inlineStr">
         <is>
-          <t>Turnstile keys not set; no WAF/DDoS layer yet.; 2026-10-23 review: Fixed: dunning SMS shared the OTP number-series budget; Turnstile and public-link spread used the proxy address; Turnstile hostname check added.</t>
+          <t>Turnstile keys not set; no WAF/DDoS layer yet.; 2026-10-23 review: Fixed: dunning SMS shared the OTP number-series budget; Turnstile and public-link spread used the proxy address; Turnstile hostname check added.; 2026-10-23 ops pass: Fixed: anonymous throttles keyed on a client-controlled X-Forwarded-For (a new value per request bypassed every limit); a Redis counter race could leave a rate-limit or lockout key with no expiry, locking a user out of the API until Redis was flushed (seen live on staging).</t>
         </is>
       </c>
     </row>
@@ -3355,7 +3355,7 @@
       </c>
       <c r="K48" s="10" t="inlineStr">
         <is>
-          <t>Counsel/DPIA and pentest pending.</t>
+          <t>Counsel/DPIA and pentest pending.; 2026-10-25 (WP, LLM plan): Covered by the DPIA draft (risks R1-R13 with controls); stale RLS/MFA facts corrected in STRIDE.md and PRODUCT_BEHAVIORS_FOR_COUNSEL.md. Left: counsel + pentest.</t>
         </is>
       </c>
     </row>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="E49" s="10" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F49" s="10" t="inlineStr">
@@ -3393,7 +3393,7 @@
       <c r="G49" s="10" t="n"/>
       <c r="H49" s="10" t="inlineStr">
         <is>
-          <t>Sentry with request_id + company_hash (no raw tenant ids); agent PII tests</t>
+          <t>Sentry with request_id + company_hash (no raw tenant ids); agent PII tests; core/log_redaction.py (RedactingFormatter on every console handler); tests/test_log_redaction.py (21 tests incl. repo-wide AST scan)</t>
         </is>
       </c>
       <c r="I49" s="10" t="n"/>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="K49" s="10" t="inlineStr">
         <is>
-          <t>No repo-wide log redaction test; check on hosted logs.</t>
+          <t>No repo-wide log redaction test; check on hosted logs.; 2026-10-24 A/B pass: Repo-wide scan found no logging call passing a password/token/OTP/key; redaction of secrets, JWTs, emails, phones, PAN, Aadhaar, cards added as a safety net, tracebacks included.</t>
         </is>
       </c>
     </row>
@@ -3506,7 +3506,7 @@
       </c>
       <c r="K51" s="10" t="inlineStr">
         <is>
-          <t>Counsel to write ToS and privacy policy.</t>
+          <t>Counsel to write ToS and privacy policy.; 2026-10-24 (D-07): first drafts for counsel in docs/legal/drafts/ (terms, privacy policy, DPA), with sub-processors and open points listed. Counsel must rewrite and approve.</t>
         </is>
       </c>
     </row>
@@ -3544,7 +3544,7 @@
       <c r="G52" s="10" t="n"/>
       <c r="H52" s="10" t="inlineStr">
         <is>
-          <t>docs/ops/INCIDENT_RESPONSE.md (CERT-In 6-hour clock); DPDP_REQUESTS.md breach fields; POSTMORTEM.md</t>
+          <t>docs/ops/INCIDENT_RESPONSE.md (CERT-In 6-hour clock); DPDP_REQUESTS.md breach fields; POSTMORTEM.md; docs/ops/TABLETOP_EXERCISES.md; ONCALL_ROSTER.md filled</t>
         </is>
       </c>
       <c r="I52" s="10" t="inlineStr">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="K52" s="10" t="inlineStr">
         <is>
-          <t>No named on-call; tabletop not held; counsel wording pending.</t>
+          <t>No named on-call; tabletop not held; counsel wording pending.; 2026-10-23 ops pass: On-call primary named (founder); no backup yet (recorded as a risk). Tabletop pack ready; not held.; 2026-10-25 (WP, LLM plan): Incident tabletop run pack (inject cards, scoring sheet, solo record) added to TABLETOP_EXERCISES.md. Left: founder runs it; backup on call.</t>
         </is>
       </c>
     </row>
@@ -3597,7 +3597,7 @@
       <c r="G53" s="10" t="n"/>
       <c r="H53" s="10" t="inlineStr">
         <is>
-          <t>Plans defined in billing module</t>
+          <t>Plans defined in billing module; docs/roadmap/SIGNOFF_PACK_2026-10-23.md B-1</t>
         </is>
       </c>
       <c r="I53" s="10" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="K53" s="10" t="inlineStr">
         <is>
-          <t>Prices not signed.</t>
+          <t>Prices not signed.; 2026-10-24 A/B pass: Plan and price proposal drafted. Awaiting founder signature.; 2026-10-25: found - seeded paid plans switch the GSTR-1/3B worksheets off (ENABLE_GSTR in FREEZE_DARK_PLAN_MODULES) while the trial has them, so an upgrading customer would lose them. Awaiting founder decision on which paid plans include them.; 2026-10-25 (D-16): every plan, Free included, now grants the GSTR-1/3B worksheets; pricing page shows it.</t>
         </is>
       </c>
     </row>
@@ -3703,7 +3703,7 @@
       <c r="G55" s="10" t="n"/>
       <c r="H55" s="10" t="inlineStr">
         <is>
-          <t>Razorpay integration (sandbox)</t>
+          <t>Razorpay integration (sandbox); 152 billing/gateway tests pass (mocked gateway)</t>
         </is>
       </c>
       <c r="I55" s="10" t="inlineStr">
@@ -3718,7 +3718,7 @@
       </c>
       <c r="K55" s="10" t="inlineStr">
         <is>
-          <t>Live Razorpay account, keys and live daily recon pending.</t>
+          <t>Live Razorpay account, keys and live daily recon pending.; 2026-10-23 ops pass: Sandbox runs skipped: no Razorpay test keys yet.</t>
         </is>
       </c>
     </row>
@@ -3956,7 +3956,7 @@
       <c r="G60" s="10" t="n"/>
       <c r="H60" s="10" t="inlineStr">
         <is>
-          <t>SaaS dunning (PAST_DUE); 3-day grace on unpaid proration</t>
+          <t>SaaS dunning (PAST_DUE); 3-day grace on unpaid proration; docs/roadmap/SIGNOFF_PACK_2026-10-23.md B-3</t>
         </is>
       </c>
       <c r="I60" s="10" t="n"/>
@@ -3967,7 +3967,7 @@
       </c>
       <c r="K60" s="10" t="inlineStr">
         <is>
-          <t>Grace-period policy not signed by founder.</t>
+          <t>Grace-period policy not signed by founder.; 2026-10-24 A/B pass: Proposal: 7-day grace (today 0) then read-only, data kept. Awaiting founder signature.</t>
         </is>
       </c>
     </row>
@@ -4088,7 +4088,7 @@
       </c>
       <c r="E63" s="10" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F63" s="10" t="inlineStr">
@@ -4099,7 +4099,7 @@
       <c r="G63" s="10" t="n"/>
       <c r="H63" s="10" t="inlineStr">
         <is>
-          <t>Per-module reviews (sales, purchase, inventory, accounting, CRM, mfg); schema constraints</t>
+          <t>Per-module reviews (sales, purchase, inventory, accounting, CRM, mfg); schema constraints; docs/architecture/SCHEMA_REVIEW_2026-10-23.md; payments migration 0046 (unique receipt/payment numbers)</t>
         </is>
       </c>
       <c r="I63" s="10" t="n"/>
@@ -4110,7 +4110,7 @@
       </c>
       <c r="K63" s="10" t="inlineStr">
         <is>
-          <t>No single signed schema review.</t>
+          <t>No single signed schema review.; 2026-10-24 A/B pass: 274 models reviewed: tenancy + RLS coverage, no float money, delete rules safe, indexes present. Fixed: receipts and supplier payments now have a DB-level unique number per company.</t>
         </is>
       </c>
     </row>
@@ -4333,7 +4333,7 @@
       </c>
       <c r="E68" s="10" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F68" s="10" t="inlineStr">
@@ -4344,7 +4344,7 @@
       <c r="G68" s="10" t="n"/>
       <c r="H68" s="10" t="inlineStr">
         <is>
-          <t>docs/ops/INDEXES.md; test_phase0_api_slas.py; test_ws08_report_performance.py</t>
+          <t>docs/ops/INDEXES.md; test_phase0_api_slas.py; test_ws08_report_performance.py; core/services/lookup_cache.py; tests/test_complete_query_budget.py; docs/architecture/SCHEMA_REVIEW_2026-10-23.md (indexes)</t>
         </is>
       </c>
       <c r="I68" s="10" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="K68" s="10" t="inlineStr">
         <is>
-          <t>Shadow books add ~50 queries to invoice Complete; reduction tracked.</t>
+          <t>Shadow books add ~50 queries to invoice Complete; reduction tracked.; 2026-10-24 A/B pass: Complete with ledger on: 151 -&gt; 146 queries (ledger overhead 49 -&gt; 44, budget-guarded). Remaining are period locks, numbering and journal writes by design; all hot lookups indexed. 1,124 money-path tests pass.</t>
         </is>
       </c>
     </row>
@@ -4408,7 +4408,7 @@
       </c>
       <c r="K69" s="10" t="inlineStr">
         <is>
-          <t>Transaction pooling deliberately not built. Not on a host yet.</t>
+          <t>Transaction pooling deliberately not built. Not on a host yet.; 2026-10-25 (WP, LLM plan): PgBouncer overlay built and tested locally (docker-compose.pgbouncer.yml, session mode, auth_query, no password on disk); role-level 30s/60s timeouts fixed a silent loss through the pool; boot guard; CI render check. Measured slower than direct on the laptop, so production starts without it (docs/ops/POSTGRES.md). Left: decide/confirm on the host.</t>
         </is>
       </c>
     </row>
@@ -4446,7 +4446,7 @@
       <c r="G70" s="10" t="n"/>
       <c r="H70" s="10" t="inlineStr">
         <is>
-          <t>seed_load_tenant; load/SEED_50K.md; dashboard p95 spec (2.8-6.0 s on laptop)</t>
+          <t>seed_load_tenant; load/SEED_50K.md; dashboard p95 spec (2.8-6.0 s on laptop); seed_load_tenant staff login; seed_draft_pool top-up</t>
         </is>
       </c>
       <c r="I70" s="10" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="K70" s="10" t="inlineStr">
         <is>
-          <t>Large-tenant run on hosted infra pending.</t>
+          <t>Large-tenant run on hosted infra pending.; 2026-10-23 ops pass: Load tenant now has a sales-staff login outside the two-step rule; seed_draft_pool no longer fails on a tenant with opening stock.</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="K71" s="10" t="inlineStr">
         <is>
-          <t>Counsel sign-off pending.</t>
+          <t>Counsel sign-off pending.; 2026-10-25 (D-13): owner-set retention for read-only workspaces (default 90 days, 30-3650), warnings 30 and 7 days ahead, tombstone erasure behind DATA_RETENTION_ENFORCE (off until counsel confirms); docs/ops/DATA_RETENTION.md, test_data_retention.py.</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4552,7 @@
       <c r="G72" s="10" t="n"/>
       <c r="H72" s="10" t="inlineStr">
         <is>
-          <t>docs/ops/SLO.md (draft)</t>
+          <t>docs/ops/SLO.md (draft); docs/roadmap/SIGNOFF_PACK_2026-10-23.md B-6; docs/ops/SLO.md</t>
         </is>
       </c>
       <c r="I72" s="10" t="inlineStr">
@@ -4567,7 +4567,7 @@
       </c>
       <c r="K72" s="10" t="inlineStr">
         <is>
-          <t>Not signed.</t>
+          <t>Not signed.; 2026-10-24 A/B pass: Proposal: sign SLO.md targets as is; keep Complete cap 30/min/company. Awaiting founder signature.; 2026-10-25 (D-11): Complete cap decided - 60 per minute per company (was 30); purchase bills stay at 30. SLO table itself still awaits signature.</t>
         </is>
       </c>
     </row>
@@ -4605,7 +4605,7 @@
       <c r="G73" s="10" t="n"/>
       <c r="H73" s="10" t="inlineStr">
         <is>
-          <t>load/k6_mixed.js, k6_slo.js, locust_smoke.py</t>
+          <t>load/k6_mixed.js, k6_slo.js, locust_smoke.py; k6 v1.8.1 installed; dry run on local staging (load/README.md)</t>
         </is>
       </c>
       <c r="I73" s="10" t="inlineStr">
@@ -4620,7 +4620,7 @@
       </c>
       <c r="K73" s="10" t="inlineStr">
         <is>
-          <t>Needs hosted staging.</t>
+          <t>Needs hosted staging.; 2026-10-23 ops pass: Scripts proven locally. Fixed: k6_slo/k6_mixed "passed" with zero work (bearer token staging never sends). Before the hosted run decide: sales_complete cap 30/min per company; one staff login per VU.; 2026-10-24: month_end.js answers the owner two-step challenge (TOTP_SECRETS); dry run on local staging passed. Left: the hosted run.; 2026-10-24 (D-10): seed_load_tenant --staff 25 and k6_mixed.js STAFF_EMAILS give each VU its own login; dry run on local staging 357 requests, 0 failed.; 2026-10-25: k6_slo.js also uses one login per VU and runs Completes at COMPLETES_PER_MIN (default 50, under the 60/min cap); k6_mixed.js writers paced the same. Local dry run: 353 requests, 0 failed, no 429s (Completes were 26% 2xx before). Hosted run still needed.</t>
         </is>
       </c>
     </row>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="K75" s="10" t="inlineStr">
         <is>
-          <t>Local staging import 10.2 s vs 10 s SLA.</t>
+          <t>2026-10-24: import commit loads only the SKUs in the file; 5,000-row catalogue upload + commit 8.7-8.9 s on Postgres, I4 gate passes on Postgres and SQLite (laptop). Left: confirm on the hosted server.; 2026-10-25: looked for more speed; the rest is Django preparing ~225,000 insert values, and bypassing the ORM is not worth the risk. Stays at 8.7-8.9 s against 10 s; confirm on the hosted server.</t>
         </is>
       </c>
     </row>
@@ -4779,7 +4779,7 @@
       </c>
       <c r="K76" s="10" t="inlineStr">
         <is>
-          <t>Needs load on hosted infra.</t>
+          <t>Needs load on hosted infra.; 2026-10-23 ops pass: No change: needs load on hosted infra.</t>
         </is>
       </c>
     </row>
@@ -4832,7 +4832,7 @@
       </c>
       <c r="K77" s="10" t="inlineStr">
         <is>
-          <t>Waits on hosted load results.</t>
+          <t>Waits on hosted load results.; 2026-10-25 (WP, LLM plan): Initial web load cut from 721.7 KB to 496.6 KB gzip (Hindi catalogue and page-help catalogue now load on demand); bundle budget 530 KB passes again. Left: hosted load results.</t>
         </is>
       </c>
     </row>
@@ -4915,7 +4915,7 @@
       <c r="G79" s="10" t="n"/>
       <c r="H79" s="10" t="inlineStr">
         <is>
-          <t>load/ scripts; load/month_end.js</t>
+          <t>load/ scripts; load/month_end.js; k6 smoke on local staging: 289 requests, 0 failed</t>
         </is>
       </c>
       <c r="I79" s="10" t="inlineStr">
@@ -4930,7 +4930,7 @@
       </c>
       <c r="K79" s="10" t="inlineStr">
         <is>
-          <t>Load and 8-hour soak need hosted staging; k6 not installed locally.; 2026-10-23 review: month_end.js fixed: could not sign in on staging (cookie-only); arrivals now spread over the window.</t>
+          <t>Load and 8-hour soak need hosted staging; k6 not installed locally.; 2026-10-23 review: month_end.js fixed: could not sign in on staging (cookie-only); arrivals now spread over the window.; 2026-10-23 ops pass: k6 is now installed locally (the note above is stale). month_end.js owners need a two-step (TOTP) step before it can run on staging; SOAK_MINUTES added for short dry runs.; 2026-10-24: month_end.js answers the owner two-step challenge (TOTP_SECRETS); dry run on local staging passed. Left: the hosted run.; 2026-10-24 (D-10): seed_load_tenant --staff 25 and k6_mixed.js STAFF_EMAILS give each VU its own login; dry run on local staging 357 requests, 0 failed.; 2026-10-25: k6_slo.js also uses one login per VU and runs Completes at COMPLETES_PER_MIN (default 50, under the 60/min cap); k6_mixed.js writers paced the same. Local dry run: 353 requests, 0 failed, no 429s (Completes were 26% 2xx before). Hosted run still needed.</t>
         </is>
       </c>
     </row>
@@ -4968,7 +4968,7 @@
       <c r="G80" s="10" t="n"/>
       <c r="H80" s="10" t="inlineStr">
         <is>
-          <t>docs/ops/WORKER_SCALE.md; queue-depth metrics and alerts</t>
+          <t>docs/ops/WORKER_SCALE.md; queue-depth metrics and alerts; docs/roadmap/SIGNOFF_PACK_2026-10-23.md B-7</t>
         </is>
       </c>
       <c r="I80" s="10" t="inlineStr">
@@ -4983,7 +4983,7 @@
       </c>
       <c r="K80" s="10" t="inlineStr">
         <is>
-          <t>Capacity numbers not signed.</t>
+          <t>Capacity numbers not signed.; 2026-10-24 A/B pass: Scale thresholds proposed (CPU, memory, DB connections, disk, Celery backlog, p95). Awaiting founder signature.</t>
         </is>
       </c>
     </row>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="K81" s="10" t="inlineStr">
         <is>
-          <t>Hosted staging and production not provisioned.</t>
+          <t>Hosted staging and production not provisioned.; 2026-10-25 (WP, LLM plan): Provider-neutral hosting kit (D-18): scripts/host/bootstrap_vm.sh (--check), render_env.sh (secret store -&gt; .env, refuses placeholders), preflight.py (PASS/FAIL incl. RLS role, timeouts, TLS, HSTS, ports open around ufw, backups, OPS_ALERT_TOKEN); first-boot checklist in HOSTED_STAGING.md. Left: pick provider and run it.</t>
         </is>
       </c>
     </row>
@@ -5089,7 +5089,7 @@
       </c>
       <c r="K82" s="10" t="inlineStr">
         <is>
-          <t>Real values and secrets manager need the host.; 2026-10-23 review: Fixed a launch blocker: VITE_TURNSTILE_SITE_KEY / VITE_GOOGLE_CLIENT_ID never reached the built web bundle (production would refuse every sign-up/OTP/reset). Set them as CD repository variables. New: EMAIL_WEBHOOK_USER/PASSWORD (were never defined, bounce webhook refused everything), PLATFORM_GST_INVOICES_FROM, TURNSTILE_ALLOWED_HOSTNAMES.</t>
+          <t>Real values and secrets manager need the host.; 2026-10-23 review: Fixed a launch blocker: VITE_TURNSTILE_SITE_KEY / VITE_GOOGLE_CLIENT_ID never reached the built web bundle (production would refuse every sign-up/OTP/reset). Set them as CD repository variables. New: EMAIL_WEBHOOK_USER/PASSWORD (were never defined, bounce webhook refused everything), PLATFORM_GST_INVOICES_FROM, TURNSTILE_ALLOWED_HOSTNAMES.; 2026-10-25 (WP, LLM plan): render_env.sh builds .env from AWS SSM / Azure KV / GCP SM / any command and refuses placeholder values; preflight checks required values. Left: real secrets on the host.</t>
         </is>
       </c>
     </row>
@@ -5142,7 +5142,7 @@
       </c>
       <c r="K83" s="10" t="inlineStr">
         <is>
-          <t>No hosted target yet.</t>
+          <t>No hosted target yet.; 2026-10-25 (WP, LLM plan): deploy-staging.yml already reads host/user/dir from the staging environment secrets; documented which secrets to create and a required reviewer. Left: a host to deploy to.</t>
         </is>
       </c>
     </row>
@@ -5293,7 +5293,7 @@
       </c>
       <c r="K86" s="10" t="inlineStr">
         <is>
-          <t>Not deployed to a host.</t>
+          <t>Not deployed to a host.; 2026-10-25 (WP, LLM plan): Kit + preflight ready; Docker-bypasses-ufw check added. Left: deploy on a host.</t>
         </is>
       </c>
     </row>
@@ -5399,7 +5399,7 @@
       </c>
       <c r="K88" s="10" t="inlineStr">
         <is>
-          <t>Hosting provider/domain not chosen.</t>
+          <t>Hosting provider/domain not chosen.; 2026-10-25 (WP, LLM plan): Preflight checks TLS validity, HSTS and HTTP-&gt;HTTPS redirect. Left: register domain and DNS.</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="K90" s="10" t="inlineStr">
         <is>
-          <t>Not yet exercised on a host.</t>
+          <t>Not yet exercised on a host.; 2026-10-25 (WP, LLM plan): First-boot-in-60-minutes runbook added to HOSTED_STAGING.md; drills README. Left: exercise on a host.</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="E91" s="10" t="inlineStr">
         <is>
-          <t>Blocked</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="F91" s="10" t="inlineStr">
@@ -5539,7 +5539,7 @@
       <c r="G91" s="10" t="n"/>
       <c r="H91" s="10" t="inlineStr">
         <is>
-          <t>Sentry wiring for API, worker and browser</t>
+          <t>Sentry wiring for API, worker and browser; self-hosted GlitchTip (docker-compose.glitchtip.yml, docs/ops/GLITCHTIP.md); /api/v1/client-errors/ relay; /admin/ops/errors/; test_error_tracker.py, test_client_error_tunnel.py</t>
         </is>
       </c>
       <c r="I91" s="10" t="inlineStr">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="K91" s="10" t="inlineStr">
         <is>
-          <t>No Sentry project/DSN.</t>
+          <t>No Sentry project/DSN.; 2026-10-23 ops pass: Free self-hosted GlitchTip replaces a paid Sentry. Live on local staging: API test event and a real browser error captured, Support ID search and ticket links work, alert email + phone push sent. Hosted run pending.; 2026-10-25: self-hosted GlitchTip integrated and tested on local staging (docs/ops/GLITCHTIP.md) - replaces the Sentry need; left: run it on the host and set the DSNs.</t>
         </is>
       </c>
     </row>
@@ -5626,7 +5626,7 @@
       </c>
       <c r="E93" s="10" t="inlineStr">
         <is>
-          <t>Blocked</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="F93" s="10" t="inlineStr">
@@ -5637,7 +5637,7 @@
       <c r="G93" s="10" t="n"/>
       <c r="H93" s="10" t="inlineStr">
         <is>
-          <t>/metrics (multiprocess); health + ready probes</t>
+          <t>/metrics (multiprocess); health + ready probes; GlitchTip uptime monitors on /api/v1/health/ and ?ready=1; check_error_tracker_task watcher</t>
         </is>
       </c>
       <c r="I93" s="10" t="inlineStr">
@@ -5652,7 +5652,7 @@
       </c>
       <c r="K93" s="10" t="inlineStr">
         <is>
-          <t>No external uptime probe or metrics service.</t>
+          <t>No external uptime probe or metrics service.; 2026-10-23 ops pass: Uptime monitors green on local staging with down/up alerts to email + ntfy push (fixed GlitchTip 6 private-IP flag). In-stack only: an external probe of the public edge and a status page are still pending.; 2026-10-24: public status page done (BB-128, /status/). Left: an external probe of the public edge and a metrics service on the host.; 2026-10-25 (WP, LLM plan): Fixed: Prometheus could not scrape the API at all (/api/v1/metrics/ 500 from a root-owned multiprocess dir); health probe now answers 503 when the DB is down. Left: external uptime probe on the host.</t>
         </is>
       </c>
     </row>
@@ -5690,7 +5690,7 @@
       <c r="G94" s="10" t="n"/>
       <c r="H94" s="10" t="inlineStr">
         <is>
-          <t>13+ alert rules with runbook sections (test_alert_rules.py); docs/ops/ALERTS.md</t>
+          <t>13+ alert rules with runbook sections (test_alert_rules.py); docs/ops/ALERTS.md; GlitchTip alert rules (new error, API down) to email + ntfy; OPS_NTFY_URL for Bizboard ops pages</t>
         </is>
       </c>
       <c r="I94" s="10" t="inlineStr">
@@ -5705,7 +5705,7 @@
       </c>
       <c r="K94" s="10" t="inlineStr">
         <is>
-          <t>No receiver/on-call phone; no test page received.; 2026-10-23 review: Fixed: SMS cap-80% page missed the first crossing after a restart; pumping alert no longer fires on the kill switch.</t>
+          <t>No receiver/on-call phone; no test page received.; 2026-10-23 review: Fixed: SMS cap-80% page missed the first crossing after a restart; pumping alert no longer fires on the kill switch.; 2026-10-23 ops pass: Alerts now reach a person on local staging: email to the founder and ntfy phone push (delivery to the topic confirmed). Prometheus rules still need test-fires on the host.; 2026-10-25: receiver chosen (D-02: founder email + ntfy phone push); left: a backup on-call person and a live alert test on the host.; 2026-10-25 (WP, LLM plan): Alert paths verified end to end locally (GlitchTip monitors 20-50 s, Prometheus worker 5 min / beat 10 min, ops relay); Alertmanager overlay + relay accepts Bearer and formats Alertmanager pages. Left: backup on call, host test.</t>
         </is>
       </c>
     </row>
@@ -5758,7 +5758,7 @@
       </c>
       <c r="K95" s="10" t="inlineStr">
         <is>
-          <t>Needs host metrics.</t>
+          <t>Needs host metrics.; 2026-10-23 ops pass: No change: needs host metrics.</t>
         </is>
       </c>
     </row>
@@ -5796,7 +5796,7 @@
       <c r="G96" s="10" t="n"/>
       <c r="H96" s="10" t="inlineStr">
         <is>
-          <t>Scheduled backups beat task (test_settings_scheduled_backup.py); backup refuses RLS-empty dump; BACKUP_ALERT.md</t>
+          <t>Scheduled backups beat task (test_settings_scheduled_backup.py); backup refuses RLS-empty dump; BACKUP_ALERT.md; glitchtip-backup service (scripts/backup.sh BACKUP_KIND=glitchtip); test_backup_scripts.py</t>
         </is>
       </c>
       <c r="I96" s="10" t="inlineStr">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="K96" s="10" t="inlineStr">
         <is>
-          <t>Off-host encrypted backups and PITR need the host.</t>
+          <t>Off-host encrypted backups and PITR need the host.; 2026-10-23 ops pass: Error-tracker database added to the nightly backup with the same encryption/off-site/retention rules; tested on local staging (163 tables).</t>
         </is>
       </c>
     </row>
@@ -5849,7 +5849,7 @@
       <c r="G97" s="10" t="n"/>
       <c r="H97" s="10" t="inlineStr">
         <is>
-          <t>docs/ops/BCP.md; DR_CADENCE.md</t>
+          <t>docs/ops/BCP.md; DR_CADENCE.md; docs/roadmap/SIGNOFF_PACK_2026-10-23.md B-8</t>
         </is>
       </c>
       <c r="I97" s="10" t="inlineStr">
@@ -5864,7 +5864,7 @@
       </c>
       <c r="K97" s="10" t="inlineStr">
         <is>
-          <t>Retention not signed.</t>
+          <t>Retention not signed.; 2026-10-24 A/B pass: Proposal: 30 daily + 12 monthly encrypted off-host, PITR 7 days. Awaiting founder signature.</t>
         </is>
       </c>
     </row>
@@ -5955,7 +5955,7 @@
       <c r="G99" s="10" t="n"/>
       <c r="H99" s="10" t="inlineStr">
         <is>
-          <t>docs/ops/SLO.md; BCP.md (draft)</t>
+          <t>docs/ops/SLO.md; BCP.md (draft); docs/roadmap/SIGNOFF_PACK_2026-10-23.md B-9</t>
         </is>
       </c>
       <c r="I99" s="10" t="inlineStr">
@@ -5970,7 +5970,7 @@
       </c>
       <c r="K99" s="10" t="inlineStr">
         <is>
-          <t>RPO/RTO not signed.</t>
+          <t>RPO/RTO not signed.; 2026-10-24 A/B pass: Proposal: RPO 15 min, RTO 4 h. Awaiting founder signature.</t>
         </is>
       </c>
     </row>
@@ -5997,7 +5997,7 @@
       </c>
       <c r="E100" s="10" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="F100" s="10" t="inlineStr">
@@ -6008,7 +6008,7 @@
       <c r="G100" s="10" t="n"/>
       <c r="H100" s="10" t="inlineStr">
         <is>
-          <t>docs/ops/DB_FAILOVER.md, INCIDENT_RESPONSE.md (runbooks only)</t>
+          <t>docs/ops/DB_FAILOVER.md, INCIDENT_RESPONSE.md (runbooks only); docs/ops/TABLETOP_EXERCISES.md (4 scenarios); DR_CADENCE.md rows</t>
         </is>
       </c>
       <c r="I100" s="10" t="inlineStr">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="K100" s="10" t="inlineStr">
         <is>
-          <t>No DR/failover drill or incident tabletop held.</t>
+          <t>No DR/failover drill or incident tabletop held.; 2026-10-23 ops pass: Tabletop pack written; the session itself is not held yet. Failover drill needs hosted Postgres.; 2026-10-25 (WP, LLM plan): Technical game day run on local staging with real alerts (docs/ops/DRILLS/2026-10-25_LOCAL_GAME_DAY.md): db/redis/beat/worker down, error, stale backup, rollback all detected/recovered; found and fixed /api/v1/metrics/ permanent 500 and health probe 500 when DB down. Tabletop run pack ready. Left: founder tabletop, failover on hosted Postgres.</t>
         </is>
       </c>
     </row>
@@ -6061,7 +6061,7 @@
       <c r="G101" s="10" t="n"/>
       <c r="H101" s="10" t="inlineStr">
         <is>
-          <t>Surface crawl of 150 routes, desktop + phone (no serious/critical axe finding); docs/UX_ACTION_ITEMS.md</t>
+          <t>docs/reviews/BB100_JOURNEY_WALKTHROUGH_2026-10-24.md: 11 journeys walked in a real browser on local staging (sale, payment, return, purchase with new supplier, quotation convert, reports, settings, help/support, Hindi, phone, sales-staff login); route sweep 138 pages desktop + phone, all flagged pages fixed; earlier surface crawl and docs/UX_ACTION_ITEMS.md; second pass 2026-10-24: phone focus/shortcut hints, staff 403 calls, purchase banner, /help render time fixed (findings F5-F9)</t>
         </is>
       </c>
       <c r="I101" s="10" t="inlineStr">
@@ -6076,7 +6076,7 @@
       </c>
       <c r="K101" s="10" t="inlineStr">
         <is>
-          <t>UX fixes not verified on a real backend by an operator.</t>
+          <t>QOS-0097; 2026-10-24: findings F1, F3, F5-F10 fixed and verified on local staging; open: F2 (GSTR-1 bills of supply, CA), F4 (Hindi FAQ), human pass on real devices.; 2026-10-24: F4 Hindi FAQ draft wired in; F2 options note for the CA written.; 2026-10-24: route sweep after all fixes, desktop and phone, 138 pages each, 0 flagged.; 2026-10-25: /help now shows its first text ~0.5 s after other pages (was 3.6 s originally).</t>
         </is>
       </c>
     </row>
@@ -6103,7 +6103,7 @@
       </c>
       <c r="E102" s="10" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F102" s="10" t="inlineStr">
@@ -6114,7 +6114,7 @@
       <c r="G102" s="10" t="n"/>
       <c r="H102" s="10" t="inlineStr">
         <is>
-          <t>Surface crawl; role matrix tests</t>
+          <t>Staff login: all 29 menu links open, none lands on limited access; blocked pages show the limited-access notice (BB100_JOURNEY_WALKTHROUGH_2026-10-24.md). Scroll regions keyboard-focusable (a11y/scrollRegions.guard.test.ts); phone sweep 138 pages, no sideways page scroll on 12 key pages; role matrix tests; team list for assignee pickers: GET /company/members/ (id, name, role) for any active member, /company/users/ stays owner-only (test_team_members.py, LeadsPage.test.tsx)</t>
         </is>
       </c>
       <c r="I102" s="10" t="inlineStr">
@@ -6129,7 +6129,7 @@
       </c>
       <c r="K102" s="10" t="inlineStr">
         <is>
-          <t>Keyboard/touch gaps open.</t>
+          <t>2026-10-24: closed. Left for the human pass: real touch devices and screen readers (BB-100).; 2026-10-24 F10: managers and staff could reassign leads/tickets but saw an empty picker; fixed and verified live with the sales-staff login.</t>
         </is>
       </c>
     </row>
@@ -6182,7 +6182,7 @@
       </c>
       <c r="K103" s="10" t="inlineStr">
         <is>
-          <t>Real-device pass open.</t>
+          <t>Real-device pass open.; 2026-10-24: phones no longer jump past the first fields on new invoice/purchase; shortcut hints hidden on touch devices. Real-device pass still open.; 2026-10-24: phone sweep 138 pages, 0 flagged.</t>
         </is>
       </c>
     </row>
@@ -6209,7 +6209,7 @@
       </c>
       <c r="E104" s="10" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F104" s="10" t="inlineStr">
@@ -6220,7 +6220,7 @@
       <c r="G104" s="10" t="n"/>
       <c r="H104" s="10" t="inlineStr">
         <is>
-          <t>Stable error codes translated en/hi; UX waves</t>
+          <t>Every data page has loading/empty/error states (pageStates.guard.test.ts); switched-off pages show a notice, not a raw error (FeatureOffNotice, navigation/switchedOff.test.ts); Hindi strings checked for English leftovers (i18n/hiNotEnglish.test.ts); stable error codes translated en/hi</t>
         </is>
       </c>
       <c r="I104" s="10" t="inlineStr">
@@ -6235,7 +6235,7 @@
       </c>
       <c r="K104" s="10" t="inlineStr">
         <is>
-          <t>Missing states and English text in Hindi screens open.</t>
+          <t>2026-10-24: closed. FAQ answer text is still English in Hindi (finding F4, human Hindi review).; 2026-10-24: FAQ answers now show in Hindi (machine draft, 284 entries, marked unreviewed on the page); a native speaker must review.; 2026-10-25: Hindi FAQ uses the app's own Hindi for 74 on-screen labels and one word for "allocation"; native review still needed.</t>
         </is>
       </c>
     </row>
@@ -6262,7 +6262,7 @@
       </c>
       <c r="E105" s="10" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F105" s="10" t="inlineStr">
@@ -6273,7 +6273,7 @@
       <c r="G105" s="10" t="n"/>
       <c r="H105" s="10" t="inlineStr">
         <is>
-          <t>Grid loading/empty/error states; Help menu, What's new</t>
+          <t>Grid loading/empty/error states; Help menu, What's new; web/src/pages/pageStates.guard.test.ts; QOS-0098 verified (jsxLiteralRatchet, mfgGridStates, LeadFormPage tests)</t>
         </is>
       </c>
       <c r="I105" s="10" t="inlineStr">
@@ -6286,7 +6286,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="K105" s="10" t="n"/>
+      <c r="K105" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-24 A/B pass: All 173 data pages handle loading/error/empty states (one deliberate fallback documented); guard keeps it so.</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="9" t="inlineStr">
@@ -6470,7 +6474,7 @@
       </c>
       <c r="E109" s="10" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F109" s="10" t="inlineStr">
@@ -6481,7 +6485,7 @@
       <c r="G109" s="10" t="n"/>
       <c r="H109" s="10" t="inlineStr">
         <is>
-          <t>docs/help/ (IMPORT_FROM_TALLY, LEGACY_IMPORT, DATA_EXPORT_FORMAT, LIMITATIONS, WHATS_NEW)</t>
+          <t>docs/help/ (IMPORT_FROM_TALLY, LEGACY_IMPORT, DATA_EXPORT_FORMAT, LIMITATIONS, WHATS_NEW); In-app Help centre FAQ (faqContent.tsx, 250+ answers) + 16 account/subscription answers; faqAccount.test.ts; docs/pilot/FAQS.md</t>
         </is>
       </c>
       <c r="I109" s="10" t="n"/>
@@ -6492,7 +6496,7 @@
       </c>
       <c r="K109" s="10" t="inlineStr">
         <is>
-          <t>No FAQ set yet.</t>
+          <t>No FAQ set yet.; 2026-10-24 A/B pass: The "no FAQ" note was stale: 236 answers existed. Added plan change, Autopay, failed payment, Bizboard GST invoices, TDS claim, cancel, data export, Busy/Vyapar/Marg import, two-step, devices, Google, ownership, owner recovery, support, support access, checklist.</t>
         </is>
       </c>
     </row>
@@ -6528,7 +6532,11 @@
         </is>
       </c>
       <c r="G110" s="10" t="n"/>
-      <c r="H110" s="10" t="n"/>
+      <c r="H110" s="10" t="inlineStr">
+        <is>
+          <t>docs/pilot/RECRUITMENT.md §5-6</t>
+        </is>
+      </c>
       <c r="I110" s="10" t="inlineStr">
         <is>
           <t>HO-15; HO-16; QOS-0029; QOS-0030</t>
@@ -6541,7 +6549,7 @@
       </c>
       <c r="K110" s="10" t="inlineStr">
         <is>
-          <t>No beta businesses signed yet.</t>
+          <t>No beta businesses signed yet.; 2026-10-23 ops pass: Recruitment tracker and import + parallel-month procedure ready; no pilots signed.</t>
         </is>
       </c>
     </row>
@@ -6643,7 +6651,7 @@
       </c>
       <c r="K112" s="10" t="inlineStr">
         <is>
-          <t>Live account and live recon pending.</t>
+          <t>Live account and live recon pending.; 2026-10-23 ops pass: Sandbox runs skipped: no Razorpay test keys yet.</t>
         </is>
       </c>
     </row>
@@ -7088,7 +7096,7 @@
       </c>
       <c r="K121" s="10" t="inlineStr">
         <is>
-          <t>Counsel to write.</t>
+          <t>Counsel to write.; 2026-10-24 (D-07): first drafts for counsel in docs/legal/drafts/ (terms, privacy policy, DPA), with sub-processors and open points listed. Counsel must rewrite and approve.</t>
         </is>
       </c>
     </row>
@@ -7141,7 +7149,7 @@
       </c>
       <c r="K122" s="10" t="inlineStr">
         <is>
-          <t>Counsel to write.</t>
+          <t>Counsel to write.; 2026-10-24 (D-07): first drafts for counsel in docs/legal/drafts/ (terms, privacy policy, DPA), with sub-processors and open points listed. Counsel must rewrite and approve.</t>
         </is>
       </c>
     </row>
@@ -7179,7 +7187,7 @@
       <c r="G123" s="10" t="n"/>
       <c r="H123" s="10" t="inlineStr">
         <is>
-          <t>docs/ops/REFUND_CANCELLATION.md (draft); BL1 refund/credit flow; test_tds_claims_trial_guard.py (review-fix tests)</t>
+          <t>docs/ops/REFUND_CANCELLATION.md (draft); BL1 refund/credit flow; test_tds_claims_trial_guard.py (review-fix tests); docs/roadmap/SIGNOFF_PACK_2026-10-23.md B-4; docs/ops/REFUND_CANCELLATION.md (updated)</t>
         </is>
       </c>
       <c r="I123" s="10" t="inlineStr">
@@ -7194,7 +7202,7 @@
       </c>
       <c r="K123" s="10" t="inlineStr">
         <is>
-          <t>Counsel to approve.; 2026-10-23 review: Fixed: TDS refunds could be paid twice (concurrency, rollback after refund); idempotency keys added.</t>
+          <t>Counsel to approve.; 2026-10-23 review: Fixed: TDS refunds could be paid twice (concurrency, rollback after refund); idempotency keys added.; 2026-10-24 A/B pass: Policy proposal drafted; refund doc corrected (proration exists). Awaiting founder decision, then counsel wording.</t>
         </is>
       </c>
     </row>
@@ -7247,7 +7255,7 @@
       </c>
       <c r="K124" s="10" t="inlineStr">
         <is>
-          <t>Counsel review and DPIA decision pending.</t>
+          <t>Counsel review and DPIA decision pending.; 2026-10-25 (WP, LLM plan): DPIA first draft written (docs/legal/drafts/DPIA_DRAFT.md): roles, data, flows, 13 risks with controls, rights, breach; 7 questions for counsel. Left: counsel decides if mandatory and approves.</t>
         </is>
       </c>
     </row>
@@ -7391,7 +7399,7 @@
       <c r="G127" s="10" t="n"/>
       <c r="H127" s="10" t="inlineStr">
         <is>
-          <t>P0-P3 severity with SLA due dates built</t>
+          <t>P0-P3 severity with SLA due dates built; docs/roadmap/SIGNOFF_PACK_2026-10-23.md B-10</t>
         </is>
       </c>
       <c r="I127" s="10" t="inlineStr">
@@ -7406,7 +7414,7 @@
       </c>
       <c r="K127" s="10" t="inlineStr">
         <is>
-          <t>Targets not signed.</t>
+          <t>Targets not signed.; 2026-10-24 A/B pass: Severity targets proposed (P0 2 h ... P3 2 business days). Awaiting founder signature.</t>
         </is>
       </c>
     </row>
@@ -7482,7 +7490,7 @@
       </c>
       <c r="E129" s="10" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F129" s="10" t="inlineStr">
@@ -7493,7 +7501,7 @@
       <c r="G129" s="10" t="n"/>
       <c r="H129" s="10" t="inlineStr">
         <is>
-          <t>docs/ops/STATUS_COMMS.md; in-app announcement banners (CM3); breach-notice fields</t>
+          <t>docs/ops/STATUS_COMMS.md (procedures + status page section); public status page from GlitchTip uptime monitors served by nginx at /status/ (no cookies, strict CSP), auto-created by deploy/glitchtip/bootstrap.py, test in test_error_tracker.py; verified on local staging 2026-10-24 (both monitors up); in-app announcement banners (CM3); breach-notice fields</t>
         </is>
       </c>
       <c r="I129" s="10" t="inlineStr">
@@ -7508,7 +7516,7 @@
       </c>
       <c r="K129" s="10" t="inlineStr">
         <is>
-          <t>No public status page.</t>
+          <t>2026-10-24: closed. Goes public when the edge is deployed on the real domain.</t>
         </is>
       </c>
     </row>
@@ -7535,7 +7543,7 @@
       </c>
       <c r="E130" s="10" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="F130" s="10" t="inlineStr">
@@ -7557,7 +7565,7 @@
       </c>
       <c r="K130" s="10" t="inlineStr">
         <is>
-          <t>DPA and vendor contracts not reviewed by counsel.</t>
+          <t>DPA and vendor contracts not reviewed by counsel.; 2026-10-24 (D-07): first drafts for counsel in docs/legal/drafts/ (terms, privacy policy, DPA), with sub-processors and open points listed. Counsel must rewrite and approve.; 2026-10-24: DPA first draft ready for counsel (docs/legal/drafts/DATA_PROCESSING_AGREEMENT_DRAFT.md); counsel review still needed.; 2026-10-25 (WP, LLM plan): Vendor contract checklist drafted (docs/legal/drafts/VENDOR_CONTRACT_CHECKLIST.md): 14 checks per launch vendor and our DPA promises mapped to vendor terms; SUBPROCESSORS.md now lists the AI provider, Google, Cloudflare, Telegram, identity check, AA, host. Left: vendor terms + counsel.</t>
         </is>
       </c>
     </row>
@@ -7595,7 +7603,7 @@
       <c r="G131" s="10" t="n"/>
       <c r="H131" s="10" t="inlineStr">
         <is>
-          <t>docs/COMPETITIVE_ANALYSIS_BIZBOARD.md; GROWTH_OS_DECISIONS_2026-09-30.md</t>
+          <t>docs/COMPETITIVE_ANALYSIS_BIZBOARD.md; GROWTH_OS_DECISIONS_2026-09-30.md; docs/roadmap/SIGNOFF_PACK_2026-10-23.md B-11</t>
         </is>
       </c>
       <c r="I131" s="10" t="n"/>
@@ -7606,7 +7614,7 @@
       </c>
       <c r="K131" s="10" t="inlineStr">
         <is>
-          <t>Not finalised.</t>
+          <t>Not finalised.; 2026-10-24 A/B pass: Positioning statement drafted. Awaiting founder signature.</t>
         </is>
       </c>
     </row>
@@ -7693,7 +7701,7 @@
       <c r="G133" s="10" t="n"/>
       <c r="H133" s="10" t="inlineStr">
         <is>
-          <t>BUSINESS_ARCHETYPES_AND_PERSONAS.md; Growth OS 3 parallel pilots</t>
+          <t>BUSINESS_ARCHETYPES_AND_PERSONAS.md; Growth OS 3 parallel pilots; docs/roadmap/SIGNOFF_PACK_2026-10-23.md B-12</t>
         </is>
       </c>
       <c r="I133" s="10" t="n"/>
@@ -7702,7 +7710,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="K133" s="10" t="n"/>
+      <c r="K133" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-24 A/B pass: Segments and channels drafted. Awaiting founder signature.</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="9" t="inlineStr">
@@ -7727,7 +7739,7 @@
       </c>
       <c r="E134" s="10" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="F134" s="10" t="inlineStr">
@@ -7749,7 +7761,7 @@
       </c>
       <c r="K134" s="10" t="inlineStr">
         <is>
-          <t>No website or pricing page yet.</t>
+          <t>No website or pricing page yet.; 2026-10-25 (D-15): draft site and pricing page in site/ (English + Hindi home, noindex, prices marked draft); not published. Waits on signed prices, domain and approved legal pages.; 2026-10-25: pricing page now lists GST worksheets on every plan (D-16).</t>
         </is>
       </c>
     </row>
@@ -7776,7 +7788,7 @@
       </c>
       <c r="E135" s="10" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F135" s="10" t="inlineStr">
@@ -7785,7 +7797,11 @@
         </is>
       </c>
       <c r="G135" s="10" t="n"/>
-      <c r="H135" s="10" t="n"/>
+      <c r="H135" s="10" t="inlineStr">
+        <is>
+          <t>seed_demo --with-activity (tests/test_seed_demo_activity.py); docs/onboarding/DEMO_SCRIPT.md</t>
+        </is>
+      </c>
       <c r="I135" s="10" t="n"/>
       <c r="J135" s="10" t="inlineStr">
         <is>
@@ -7794,7 +7810,7 @@
       </c>
       <c r="K135" s="10" t="inlineStr">
         <is>
-          <t>Practice company with demo data deferred (G-04).</t>
+          <t>Practice company with demo data deferred (G-04).; 2026-10-24 A/B pass: Demo company with 3 months of invoices, receipts (paid/part/unpaid) and a return; 20-minute demo script with honest answers. In-product practice company (G-04) stays deferred.</t>
         </is>
       </c>
     </row>
@@ -7832,7 +7848,7 @@
       <c r="G136" s="10" t="n"/>
       <c r="H136" s="10" t="inlineStr">
         <is>
-          <t>FULL_SPECTRUM_PERSONA_VALIDATION_PLAN.md; SR2 done-whens (zero unexplained recon, a day without an engineer)</t>
+          <t>FULL_SPECTRUM_PERSONA_VALIDATION_PLAN.md; SR2 done-whens (zero unexplained recon, a day without an engineer); docs/roadmap/SIGNOFF_PACK_2026-10-23.md B-13</t>
         </is>
       </c>
       <c r="I136" s="10" t="n"/>
@@ -7843,7 +7859,7 @@
       </c>
       <c r="K136" s="10" t="inlineStr">
         <is>
-          <t>Not agreed with pilot customers.</t>
+          <t>Not agreed with pilot customers.; 2026-10-24 A/B pass: Six acceptance criteria drafted. Awaiting founder signature and pilot agreement.</t>
         </is>
       </c>
     </row>
@@ -7870,7 +7886,7 @@
       </c>
       <c r="E137" s="10" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F137" s="10" t="inlineStr">
@@ -7881,7 +7897,7 @@
       <c r="G137" s="10" t="n"/>
       <c r="H137" s="10" t="inlineStr">
         <is>
-          <t>docs/ops/FEEDBACK_TRIAGE.md; in-app support tickets</t>
+          <t>docs/ops/FEEDBACK_TRIAGE.md; in-app support tickets; NPS prompt + CSAT on resolved support requests behind ENABLE_SATISFACTION_SURVEY (off by default); staff read answers and NPS in Django admin; test_satisfaction_survey.py, NpsPrompt.test.tsx; verified live on local staging</t>
         </is>
       </c>
       <c r="I137" s="10" t="n"/>
@@ -7892,7 +7908,7 @@
       </c>
       <c r="K137" s="10" t="inlineStr">
         <is>
-          <t>NPS/CSAT deferred (P-04).</t>
+          <t>NPS/CSAT deferred (P-04).; 2026-10-24 (D-08): survey built, P-04 deferral lifted. Left: turn it on per company once pilots start.; 2026-10-24: closed - in-app NPS and support CSAT built and verified, answers in Django admin, triage in FEEDBACK_TRIAGE.md. Switch it on per company when pilots start.</t>
         </is>
       </c>
     </row>
@@ -7930,7 +7946,7 @@
       <c r="G138" s="10" t="n"/>
       <c r="H138" s="10" t="inlineStr">
         <is>
-          <t>Trial expiry write-block; checkout; trial-to-paid metric</t>
+          <t>Trial expiry write-block; checkout; trial-to-paid metric; docs/roadmap/SIGNOFF_PACK_2026-10-23.md B-5</t>
         </is>
       </c>
       <c r="I138" s="10" t="inlineStr">
@@ -7945,7 +7961,7 @@
       </c>
       <c r="K138" s="10" t="inlineStr">
         <is>
-          <t>Process not signed.</t>
+          <t>Process not signed.; 2026-10-24 A/B pass: Trial-to-paid process drafted (no automatic welcome email yet; founder sends). Awaiting founder signature.</t>
         </is>
       </c>
     </row>
@@ -8021,7 +8037,7 @@
       </c>
       <c r="E140" s="10" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F140" s="10" t="inlineStr">
@@ -8039,7 +8055,7 @@
       </c>
       <c r="K140" s="10" t="inlineStr">
         <is>
-          <t>Referral programme planned after launch (G-03).</t>
+          <t>Referral programme planned after launch (G-03).; 2026-10-23 ops pass: Deferred to after launch by plan (G-03); not a launch blocker.; 2026-10-24: feedback half done (NPS/CSAT, BB-136); referral programme still deferred to after launch (G-03).; 2026-10-25 (WP, LLM plan): Bizboard referral programme built behind ENABLE_SAAS_REFERRALS (off, D-19): link + WhatsApp share in Settings &gt; Billing, ?ref= on password and Google sign-up, daily qualification on paid activation, same-business and daily-cap guards, reward recorded only and settled by staff in admin (docs/ops/REFERRALS.md). RLS migration core 0074; test_saas_referrals.py 11 + 2 Postgres app-role tests pass. Feedback half done earlier (BB-136).</t>
         </is>
       </c>
     </row>
@@ -8092,7 +8108,7 @@
       </c>
       <c r="K141" s="10" t="inlineStr">
         <is>
-          <t>CA sign-offs and real-user runs still open.; 2026-10-23 review: Deep review of the SaaS Phase 1+2 code: about 130 candidates, real ones fixed with tests.</t>
+          <t>CA sign-offs and real-user runs still open.; 2026-10-23 review: Deep review of the SaaS Phase 1+2 code: about 130 candidates, real ones fixed with tests.; 2026-10-24: quote/order GST total could differ from the invoice (BB-100 F1) - fixed for quotations, sales and purchase orders.</t>
         </is>
       </c>
     </row>
@@ -8145,7 +8161,7 @@
       </c>
       <c r="K142" s="10" t="inlineStr">
         <is>
-          <t>Not on hosted staging; tree partly uncommitted.</t>
+          <t>Not on hosted staging; tree partly uncommitted.; 2026-10-25 (WP, LLM plan): CI half run locally (see BB-017). Left: commit + hosted staging.</t>
         </is>
       </c>
     </row>
@@ -8183,7 +8199,7 @@
       <c r="G143" s="10" t="n"/>
       <c r="H143" s="10" t="inlineStr">
         <is>
-          <t>GL parity invariants; restore drill sweep clean</t>
+          <t>GL parity invariants; restore drill sweep clean; docs/pilot/RECRUITMENT.md §6 (compare_trial_balance steps)</t>
         </is>
       </c>
       <c r="I143" s="10" t="inlineStr">
@@ -8198,7 +8214,7 @@
       </c>
       <c r="K143" s="10" t="inlineStr">
         <is>
-          <t>Parallel month with real pilots (compare_trial_balance) pending.</t>
+          <t>Parallel month with real pilots (compare_trial_balance) pending.; 2026-10-23 ops pass: Parallel-month procedure written; needs real pilots.</t>
         </is>
       </c>
     </row>
@@ -8251,7 +8267,7 @@
       </c>
       <c r="K144" s="10" t="inlineStr">
         <is>
-          <t>Hosted run and pentest pending.; 2026-10-23 review: Postgres-only RLS regressions from the review added.</t>
+          <t>Hosted run and pentest pending.; 2026-10-23 review: Postgres-only RLS regressions from the review added.; 2026-10-24: Postgres-only suites (row-level security, concurrency, tenancy) re-run on a fresh local Postgres: 543 passed, 1 skipped. Still to run on the hosted database.; 2026-10-25 (WP, LLM plan): Same as BB-029 (local probe clean). Left: hosted run and pentest.</t>
         </is>
       </c>
     </row>
@@ -8304,7 +8320,7 @@
       </c>
       <c r="K145" s="10" t="inlineStr">
         <is>
-          <t>Independent pentest not done.</t>
+          <t>Independent pentest not done.; 2026-10-25 (WP, LLM plan): Local scan findings fixed (headers, JSON API errors, 3 high npm advisories: zod 4.6.7, follow-redirects 1.16.1, fast-uri 3.1.9; pip-audit clean). Left: pentest findings and their fixes.</t>
         </is>
       </c>
     </row>
@@ -8384,7 +8400,7 @@
       </c>
       <c r="E147" s="10" t="inlineStr">
         <is>
-          <t>Blocked</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="F147" s="10" t="inlineStr">
@@ -8395,7 +8411,7 @@
       <c r="G147" s="10" t="n"/>
       <c r="H147" s="10" t="inlineStr">
         <is>
-          <t>Alert rules + runbooks built</t>
+          <t>Alert rules + runbooks built; GlitchTip error tracking + alerts live on local staging; on-call primary named</t>
         </is>
       </c>
       <c r="I147" s="10" t="inlineStr">
@@ -8410,7 +8426,7 @@
       </c>
       <c r="K147" s="10" t="inlineStr">
         <is>
-          <t>No Sentry, metrics service or on-call.</t>
+          <t>No Sentry, metrics service or on-call.; 2026-10-23 ops pass: Error tracking, alerts and an on-call person now exist (local staging). Hosted verification and metrics service pending.</t>
         </is>
       </c>
     </row>
@@ -8448,7 +8464,7 @@
       <c r="G148" s="10" t="n"/>
       <c r="H148" s="10" t="inlineStr">
         <is>
-          <t>Billing flows tested in repo</t>
+          <t>Billing flows tested in repo; 152 billing/gateway tests pass (mocked gateway)</t>
         </is>
       </c>
       <c r="I148" s="10" t="inlineStr">
@@ -8463,7 +8479,7 @@
       </c>
       <c r="K148" s="10" t="inlineStr">
         <is>
-          <t>Razorpay sandbox runs and live account pending.</t>
+          <t>Razorpay sandbox runs and live account pending.; 2026-10-23 ops pass: Sandbox runs skipped: no Razorpay test keys yet.</t>
         </is>
       </c>
     </row>
@@ -8499,7 +8515,11 @@
         </is>
       </c>
       <c r="G149" s="10" t="n"/>
-      <c r="H149" s="10" t="n"/>
+      <c r="H149" s="10" t="inlineStr">
+        <is>
+          <t>docs/pilot/RECRUITMENT.md §5-6</t>
+        </is>
+      </c>
       <c r="I149" s="10" t="inlineStr">
         <is>
           <t>HO-15</t>
@@ -8512,7 +8532,7 @@
       </c>
       <c r="K149" s="10" t="inlineStr">
         <is>
-          <t>No pilots signed.</t>
+          <t>No pilots signed.; 2026-10-23 ops pass: Recruitment tracker and import + parallel-month procedure ready; no pilots signed.</t>
         </is>
       </c>
     </row>
@@ -8550,7 +8570,7 @@
       <c r="G150" s="10" t="n"/>
       <c r="H150" s="10" t="inlineStr">
         <is>
-          <t>Runbooks: INCIDENT_RESPONSE, HYPERCARE, ONCALL_ROSTER (template), rollback workflow</t>
+          <t>Runbooks: INCIDENT_RESPONSE, HYPERCARE, ONCALL_ROSTER (template), rollback workflow; ONCALL_ROSTER.md (primary named)</t>
         </is>
       </c>
       <c r="I150" s="10" t="inlineStr">
@@ -8565,7 +8585,7 @@
       </c>
       <c r="K150" s="10" t="inlineStr">
         <is>
-          <t>On-call not named; rollback drill not done.</t>
+          <t>On-call not named; rollback drill not done.; 2026-10-23 ops pass: On-call primary named; no backup. Rollback drill still not done.; 2026-10-25 (WP, LLM plan): Rollback drill on local staging: 142 s back, 133 s forward; alerts verified. Left: on-call backup, host drill.</t>
         </is>
       </c>
     </row>
@@ -8603,7 +8623,7 @@
       <c r="G151" s="10" t="n"/>
       <c r="H151" s="10" t="inlineStr">
         <is>
-          <t>docs/ops/RISK_REGISTER.md; SAAS_READINESS_HANDOVER_2026-10-22.md</t>
+          <t>docs/ops/RISK_REGISTER.md; SAAS_READINESS_HANDOVER_2026-10-22.md; docs/ops/RISK_REGISTER.md (refreshed, 18 risks + 12-gate launch approval sheet)</t>
         </is>
       </c>
       <c r="I151" s="10" t="n"/>
@@ -8614,7 +8634,7 @@
       </c>
       <c r="K151" s="10" t="inlineStr">
         <is>
-          <t>Launch approval not given.</t>
+          <t>Launch approval not given.; 2026-10-24 A/B pass: Register refreshed and launch approval sheet added. Awaiting founder decisions per risk and signature.</t>
         </is>
       </c>
     </row>
